--- a/public/planilhas/avarias.xlsx
+++ b/public/planilhas/avarias.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliaquirino\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B291191A-7D2F-497E-8431-D26A4BFABA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0CF98C3-B15B-4112-A381-CADBA012031A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D7FD4738-B4FC-4B28-B1E7-9E2BE6FF9EA6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{8A8E9052-EDB1-4EDE-91D8-395DA635B3B8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="avarias" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7127" uniqueCount="1719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7653" uniqueCount="1810">
   <si>
     <t>Data/Hora</t>
   </si>
@@ -5181,16 +5181,289 @@
     <t>VOL CX VOL 2 COZINHA NINA - BALCÃO 3 PTS 1,270X0,515X0,135 - AMENDOA CLEAN/BRANCO</t>
   </si>
   <si>
+    <t>21/09/2026 10:43:22</t>
+  </si>
+  <si>
+    <t>05-1-10</t>
+  </si>
+  <si>
+    <t>PREGO NO PALETE</t>
+  </si>
+  <si>
+    <t>21/09/2026 13:24:33</t>
+  </si>
+  <si>
+    <t>21/09/2026 13:36:39</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:15:32</t>
+  </si>
+  <si>
+    <t>30-6-10</t>
+  </si>
+  <si>
+    <t>2321</t>
+  </si>
+  <si>
+    <t>ESPELHO</t>
+  </si>
+  <si>
+    <t>VOL CX ESPELHO C/1 ESP 1668X874X3 C/4 SUP CROMADO 1,710X0,982X0,047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPELHO QUEBRADO </t>
+  </si>
+  <si>
     <t>22/09/2026 08:33:35</t>
   </si>
   <si>
+    <t>22/09/2026 08:42:44</t>
+  </si>
+  <si>
+    <t>17-17-10</t>
+  </si>
+  <si>
+    <t>22/09/2026 09:59:07</t>
+  </si>
+  <si>
+    <t>31-1-10</t>
+  </si>
+  <si>
+    <t>2186</t>
+  </si>
+  <si>
+    <t>VOL CX ESPELHO C/1 ESP 695X300X3 0,798X0,347X0,026</t>
+  </si>
+  <si>
+    <t>22/09/2026 10:21:22</t>
+  </si>
+  <si>
+    <t>VOL CX MESA BASE 1,60/1,70 SINTONIA 1,030X0,495X0,072 - AMENDOA CLEAN/OFF WH</t>
+  </si>
+  <si>
+    <t>VOL CX MESA BASE 1,60/1,70 SINTONIA 1,030X0,495X0,072</t>
+  </si>
+  <si>
+    <t>22/09/2026 13:33:20</t>
+  </si>
+  <si>
+    <t>VOL CX PAINEL CAMA CASAL 1,40 LOOP 2025 1,535X0,730X0,117 - AMENDOA CLEAN#CORANO BEGE</t>
+  </si>
+  <si>
+    <t>VOL CX PAINEL CAMA CASAL 1,40 LOOP 2025 1,535X0,730X0,117</t>
+  </si>
+  <si>
+    <t>MOLHADO</t>
+  </si>
+  <si>
     <t>22/09/2026 13:39:21</t>
   </si>
   <si>
+    <t>22/09/2026 15:45:42</t>
+  </si>
+  <si>
+    <t>37-2-10</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:46:22</t>
+  </si>
+  <si>
     <t>22/09/2026 15:52:10</t>
   </si>
   <si>
     <t>VOL CX PES ATHENAS SOLT 0,90 PLUS 1,210X0,275X0,100</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:00:50</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:06:55</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:10:27</t>
+  </si>
+  <si>
+    <t>23/09/2026 02:07:53</t>
+  </si>
+  <si>
+    <t>23/09/2026 07:37:44</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:15:34</t>
+  </si>
+  <si>
+    <t>30-12-40</t>
+  </si>
+  <si>
+    <t>216.16129</t>
+  </si>
+  <si>
+    <t>VOL CX CADEIRA APOGEU/CAMINI/LOTUS/RAYLA C/2 - FRASSINO</t>
+  </si>
+  <si>
+    <t>VOL CX CADEIRA APOGEU/CAMINI/LOTUS/RAYLA C/2</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:27:07</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:31:41</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:48:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 10:06:40</t>
+  </si>
+  <si>
+    <t>23/09/2026 13:01:17</t>
+  </si>
+  <si>
+    <t>23/09/2026 13:42:37</t>
+  </si>
+  <si>
+    <t>40-1-10</t>
+  </si>
+  <si>
+    <t>VOL CX ASSENTO/ENCOSTO CAD APOGEU/TESSERA C/20,585X0,370X0,430 - LINHO RINZAI BEGE</t>
+  </si>
+  <si>
+    <t>23/09/2026 13:46:14</t>
+  </si>
+  <si>
+    <t>36-11-10</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:48:09</t>
+  </si>
+  <si>
+    <t>25-13-40</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:12:43</t>
+  </si>
+  <si>
+    <t>34-28-10</t>
+  </si>
+  <si>
+    <t>23/09/2026 23:08:07</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:17:04</t>
+  </si>
+  <si>
+    <t>24-13-10</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:47:56</t>
+  </si>
+  <si>
+    <t>33-14-10</t>
+  </si>
+  <si>
+    <t>85124.46118</t>
+  </si>
+  <si>
+    <t>VOL CX BASE MESA 1,20 SINTONIA 0,803X0,495X0,092 - AMENDOA CLEAN/OFF WH</t>
+  </si>
+  <si>
+    <t>VOL CX BASE MESA 1,20 SINTONIA 0,803X0,495X0,092</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:30:21</t>
+  </si>
+  <si>
+    <t>24/09/2026 10:32:42</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:41:15</t>
+  </si>
+  <si>
+    <t>05-9-10</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:15:32</t>
+  </si>
+  <si>
+    <t>08-16-10</t>
+  </si>
+  <si>
+    <t>25/09/2026 08:49:46</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:08:23</t>
+  </si>
+  <si>
+    <t>10-12-10</t>
+  </si>
+  <si>
+    <t>25/09/2026 10:24:34</t>
+  </si>
+  <si>
+    <t>25/09/2026 11:19:47</t>
+  </si>
+  <si>
+    <t>25/09/2026 12:57:25</t>
+  </si>
+  <si>
+    <t>05-5-10</t>
+  </si>
+  <si>
+    <t>25/09/2026 13:02:16</t>
+  </si>
+  <si>
+    <t>20-10-10</t>
+  </si>
+  <si>
+    <t>2103.13945</t>
+  </si>
+  <si>
+    <t>VOL CX GR 6 PTS ARIES 2021 LAT 2,440X0,510X0,055 - AMENDOA CLEAN</t>
+  </si>
+  <si>
+    <t>VOL CX GR 6 PTS ARIES 2021 LAT 2,440X0,510X0,055</t>
+  </si>
+  <si>
+    <t>25/09/2026 13:19:51</t>
+  </si>
+  <si>
+    <t>25/09/2026 13:35:26</t>
+  </si>
+  <si>
+    <t>25/09/2026 13:35:48</t>
+  </si>
+  <si>
+    <t>25/09/2026 13:36:01</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:56:05</t>
+  </si>
+  <si>
+    <t>12-17-10</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:50:29</t>
+  </si>
+  <si>
+    <t>14-4-10</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:55:08</t>
+  </si>
+  <si>
+    <t>25/09/2026 16:00:50</t>
+  </si>
+  <si>
+    <t>SEPARAÇÃO</t>
+  </si>
+  <si>
+    <t>25/09/2026 16:12:34</t>
+  </si>
+  <si>
+    <t>25/09/2026 20:47:53</t>
+  </si>
+  <si>
+    <t>07-11-10</t>
   </si>
 </sst>
 </file>
@@ -5645,8 +5918,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D1D49E-25E7-4B8C-9B6B-E3E61D28CC97}">
-  <dimension ref="A1:M648"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9D13CB-C288-4589-9886-E5967C5BED26}">
+  <dimension ref="A1:M696"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -32090,7 +32363,7 @@
         <v>1715</v>
       </c>
       <c r="B646" s="5">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="C646" s="5" t="s">
         <v>1650</v>
@@ -32099,7 +32372,7 @@
         <v>554</v>
       </c>
       <c r="E646" t="s">
-        <v>1113</v>
+        <v>1716</v>
       </c>
       <c r="F646" t="s">
         <v>17</v>
@@ -32108,30 +32381,30 @@
         <v>1</v>
       </c>
       <c r="H646" t="s">
-        <v>1114</v>
+        <v>1037</v>
       </c>
       <c r="I646" t="s">
         <v>19</v>
       </c>
       <c r="J646" t="s">
-        <v>1115</v>
+        <v>1038</v>
       </c>
       <c r="K646" t="s">
-        <v>589</v>
+        <v>860</v>
       </c>
       <c r="L646" t="s">
         <v>38</v>
       </c>
       <c r="M646" s="6" t="s">
-        <v>23</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="647" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A647" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="B647" s="5">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="C647" s="5" t="s">
         <v>1650</v>
@@ -32140,72 +32413,2034 @@
         <v>1094</v>
       </c>
       <c r="E647" t="s">
+        <v>885</v>
+      </c>
+      <c r="F647" t="s">
+        <v>17</v>
+      </c>
+      <c r="G647">
+        <v>1</v>
+      </c>
+      <c r="H647" t="s">
+        <v>369</v>
+      </c>
+      <c r="I647" t="s">
+        <v>19</v>
+      </c>
+      <c r="J647" t="s">
+        <v>370</v>
+      </c>
+      <c r="K647" t="s">
+        <v>371</v>
+      </c>
+      <c r="L647" t="s">
+        <v>38</v>
+      </c>
+      <c r="M647" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A648" s="4" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B648" s="5">
+        <v>46286</v>
+      </c>
+      <c r="C648" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D648" t="s">
+        <v>64</v>
+      </c>
+      <c r="E648" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F648" t="s">
+        <v>17</v>
+      </c>
+      <c r="G648">
+        <v>1</v>
+      </c>
+      <c r="H648" t="s">
+        <v>130</v>
+      </c>
+      <c r="I648" t="s">
+        <v>19</v>
+      </c>
+      <c r="J648" t="s">
+        <v>131</v>
+      </c>
+      <c r="K648" t="s">
+        <v>132</v>
+      </c>
+      <c r="L648" t="s">
+        <v>38</v>
+      </c>
+      <c r="M648" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A649" s="4" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B649" s="5">
+        <v>46286</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D649" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E649" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F649" t="s">
+        <v>17</v>
+      </c>
+      <c r="G649">
+        <v>1</v>
+      </c>
+      <c r="H649" t="s">
+        <v>1722</v>
+      </c>
+      <c r="I649" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J649" t="s">
+        <v>1724</v>
+      </c>
+      <c r="K649" t="s">
+        <v>1724</v>
+      </c>
+      <c r="M649" s="6" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A650" s="4" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B650" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C650" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D650" t="s">
+        <v>554</v>
+      </c>
+      <c r="E650" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F650" t="s">
+        <v>17</v>
+      </c>
+      <c r="G650">
+        <v>1</v>
+      </c>
+      <c r="H650" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I650" t="s">
+        <v>19</v>
+      </c>
+      <c r="J650" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K650" t="s">
+        <v>589</v>
+      </c>
+      <c r="L650" t="s">
+        <v>38</v>
+      </c>
+      <c r="M650" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A651" s="4" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B651" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D651" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E651" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F651" t="s">
+        <v>17</v>
+      </c>
+      <c r="G651">
+        <v>1</v>
+      </c>
+      <c r="H651" t="s">
+        <v>841</v>
+      </c>
+      <c r="I651" t="s">
+        <v>19</v>
+      </c>
+      <c r="J651" t="s">
+        <v>842</v>
+      </c>
+      <c r="K651" t="s">
+        <v>61</v>
+      </c>
+      <c r="L651" t="s">
+        <v>22</v>
+      </c>
+      <c r="M651" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A652" s="4" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B652" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C652" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D652" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E652" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F652" t="s">
+        <v>17</v>
+      </c>
+      <c r="G652">
+        <v>2</v>
+      </c>
+      <c r="H652" t="s">
+        <v>1731</v>
+      </c>
+      <c r="I652" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J652" t="s">
+        <v>1732</v>
+      </c>
+      <c r="K652" t="s">
+        <v>1732</v>
+      </c>
+      <c r="M652" s="6" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A653" s="4" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B653" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D653" t="s">
+        <v>179</v>
+      </c>
+      <c r="E653" t="s">
+        <v>986</v>
+      </c>
+      <c r="F653" t="s">
+        <v>17</v>
+      </c>
+      <c r="G653">
+        <v>1</v>
+      </c>
+      <c r="H653" t="s">
+        <v>919</v>
+      </c>
+      <c r="I653" t="s">
+        <v>242</v>
+      </c>
+      <c r="J653" t="s">
+        <v>1734</v>
+      </c>
+      <c r="K653" t="s">
+        <v>1735</v>
+      </c>
+      <c r="L653" t="s">
+        <v>62</v>
+      </c>
+      <c r="M653" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A654" s="4" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B654" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C654" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D654" t="s">
+        <v>33</v>
+      </c>
+      <c r="E654" t="s">
+        <v>532</v>
+      </c>
+      <c r="F654" t="s">
+        <v>17</v>
+      </c>
+      <c r="G654">
+        <v>1</v>
+      </c>
+      <c r="H654" t="s">
+        <v>533</v>
+      </c>
+      <c r="I654" t="s">
+        <v>28</v>
+      </c>
+      <c r="J654" t="s">
+        <v>1737</v>
+      </c>
+      <c r="K654" t="s">
+        <v>1738</v>
+      </c>
+      <c r="L654" t="s">
+        <v>536</v>
+      </c>
+      <c r="M654" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A655" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B655" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E655" t="s">
         <v>504</v>
       </c>
-      <c r="F647" t="s">
-        <v>17</v>
-      </c>
-      <c r="G647">
+      <c r="F655" t="s">
+        <v>17</v>
+      </c>
+      <c r="G655">
         <v>2</v>
       </c>
-      <c r="H647" t="s">
+      <c r="H655" t="s">
         <v>1370</v>
       </c>
-      <c r="I647" t="s">
-        <v>19</v>
-      </c>
-      <c r="J647" t="s">
+      <c r="I655" t="s">
+        <v>19</v>
+      </c>
+      <c r="J655" t="s">
         <v>1371</v>
       </c>
-      <c r="K647" t="s">
+      <c r="K655" t="s">
         <v>1372</v>
       </c>
-      <c r="L647" t="s">
-        <v>38</v>
-      </c>
-      <c r="M647" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A648" s="7" t="s">
+      <c r="L655" t="s">
+        <v>38</v>
+      </c>
+      <c r="M655" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A656" s="4" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B656" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C656" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D656" t="s">
+        <v>996</v>
+      </c>
+      <c r="E656" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F656" t="s">
+        <v>17</v>
+      </c>
+      <c r="G656">
+        <v>1</v>
+      </c>
+      <c r="H656" t="s">
+        <v>374</v>
+      </c>
+      <c r="I656" t="s">
+        <v>19</v>
+      </c>
+      <c r="J656" t="s">
+        <v>375</v>
+      </c>
+      <c r="K656" t="s">
+        <v>376</v>
+      </c>
+      <c r="L656" t="s">
+        <v>22</v>
+      </c>
+      <c r="M656" s="6" t="s">
         <v>1717</v>
       </c>
-      <c r="B648" s="8">
+    </row>
+    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A657" s="4" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B657" s="5">
         <v>46287</v>
       </c>
-      <c r="C648" s="8" t="s">
+      <c r="C657" s="5" t="s">
         <v>1650</v>
       </c>
-      <c r="D648" s="9" t="s">
+      <c r="D657" t="s">
+        <v>996</v>
+      </c>
+      <c r="E657" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F657" t="s">
+        <v>17</v>
+      </c>
+      <c r="G657">
+        <v>1</v>
+      </c>
+      <c r="H657" t="s">
+        <v>374</v>
+      </c>
+      <c r="I657" t="s">
+        <v>19</v>
+      </c>
+      <c r="J657" t="s">
+        <v>375</v>
+      </c>
+      <c r="K657" t="s">
+        <v>376</v>
+      </c>
+      <c r="L657" t="s">
+        <v>22</v>
+      </c>
+      <c r="M657" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A658" s="4" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B658" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C658" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D658" t="s">
         <v>33</v>
       </c>
-      <c r="E648" s="9" t="s">
+      <c r="E658" t="s">
         <v>660</v>
       </c>
-      <c r="F648" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G648" s="9">
-        <v>1</v>
-      </c>
-      <c r="H648" s="9" t="s">
+      <c r="F658" t="s">
+        <v>17</v>
+      </c>
+      <c r="G658">
+        <v>1</v>
+      </c>
+      <c r="H658" t="s">
         <v>661</v>
       </c>
-      <c r="I648" s="9" t="s">
+      <c r="I658" t="s">
         <v>28</v>
       </c>
-      <c r="J648" s="9" t="s">
+      <c r="J658" t="s">
         <v>662</v>
       </c>
-      <c r="K648" s="9" t="s">
-        <v>1718</v>
-      </c>
-      <c r="L648" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M648" s="10" t="s">
-        <v>23</v>
+      <c r="K658" t="s">
+        <v>1745</v>
+      </c>
+      <c r="L658" t="s">
+        <v>38</v>
+      </c>
+      <c r="M658" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A659" s="4" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B659" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D659" t="s">
+        <v>91</v>
+      </c>
+      <c r="E659" t="s">
+        <v>339</v>
+      </c>
+      <c r="F659" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659">
+        <v>1</v>
+      </c>
+      <c r="H659" t="s">
+        <v>340</v>
+      </c>
+      <c r="I659" t="s">
+        <v>19</v>
+      </c>
+      <c r="J659" t="s">
+        <v>341</v>
+      </c>
+      <c r="K659" t="s">
+        <v>342</v>
+      </c>
+      <c r="L659" t="s">
+        <v>38</v>
+      </c>
+      <c r="M659" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A660" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B660" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C660" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D660" t="s">
+        <v>128</v>
+      </c>
+      <c r="E660" t="s">
+        <v>954</v>
+      </c>
+      <c r="F660" t="s">
+        <v>17</v>
+      </c>
+      <c r="G660">
+        <v>2</v>
+      </c>
+      <c r="H660" t="s">
+        <v>1653</v>
+      </c>
+      <c r="I660" t="s">
+        <v>28</v>
+      </c>
+      <c r="J660" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K660" t="s">
+        <v>89</v>
+      </c>
+      <c r="L660" t="s">
+        <v>38</v>
+      </c>
+      <c r="M660" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A661" s="4" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B661" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D661" t="s">
+        <v>128</v>
+      </c>
+      <c r="E661" t="s">
+        <v>687</v>
+      </c>
+      <c r="F661" t="s">
+        <v>17</v>
+      </c>
+      <c r="G661">
+        <v>1</v>
+      </c>
+      <c r="H661" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I661" t="s">
+        <v>28</v>
+      </c>
+      <c r="J661" t="s">
+        <v>1435</v>
+      </c>
+      <c r="K661" t="s">
+        <v>213</v>
+      </c>
+      <c r="L661" t="s">
+        <v>62</v>
+      </c>
+      <c r="M661" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A662" s="4" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B662" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C662" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D662" t="s">
+        <v>128</v>
+      </c>
+      <c r="E662" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F662" t="s">
+        <v>17</v>
+      </c>
+      <c r="G662">
+        <v>1</v>
+      </c>
+      <c r="H662" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I662" t="s">
+        <v>19</v>
+      </c>
+      <c r="J662" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K662" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L662" t="s">
+        <v>38</v>
+      </c>
+      <c r="M662" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A663" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B663" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D663" t="s">
+        <v>64</v>
+      </c>
+      <c r="E663" t="s">
+        <v>163</v>
+      </c>
+      <c r="F663" t="s">
+        <v>17</v>
+      </c>
+      <c r="G663">
+        <v>1</v>
+      </c>
+      <c r="H663" t="s">
+        <v>962</v>
+      </c>
+      <c r="I663" t="s">
+        <v>19</v>
+      </c>
+      <c r="J663" t="s">
+        <v>963</v>
+      </c>
+      <c r="K663" t="s">
+        <v>964</v>
+      </c>
+      <c r="L663" t="s">
+        <v>38</v>
+      </c>
+      <c r="M663" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A664" s="4" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B664" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C664" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D664" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E664" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F664" t="s">
+        <v>17</v>
+      </c>
+      <c r="G664">
+        <v>1</v>
+      </c>
+      <c r="H664" t="s">
+        <v>1753</v>
+      </c>
+      <c r="I664" t="s">
+        <v>242</v>
+      </c>
+      <c r="J664" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K664" t="s">
+        <v>1755</v>
+      </c>
+      <c r="L664" t="s">
+        <v>249</v>
+      </c>
+      <c r="M664" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A665" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B665" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D665" t="s">
+        <v>378</v>
+      </c>
+      <c r="E665" t="s">
+        <v>514</v>
+      </c>
+      <c r="F665" t="s">
+        <v>17</v>
+      </c>
+      <c r="G665">
+        <v>1</v>
+      </c>
+      <c r="H665" t="s">
+        <v>59</v>
+      </c>
+      <c r="I665" t="s">
+        <v>19</v>
+      </c>
+      <c r="J665" t="s">
+        <v>60</v>
+      </c>
+      <c r="K665" t="s">
+        <v>61</v>
+      </c>
+      <c r="L665" t="s">
+        <v>62</v>
+      </c>
+      <c r="M665" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A666" s="4" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B666" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C666" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D666" t="s">
+        <v>64</v>
+      </c>
+      <c r="E666" t="s">
+        <v>65</v>
+      </c>
+      <c r="F666" t="s">
+        <v>17</v>
+      </c>
+      <c r="G666">
+        <v>1</v>
+      </c>
+      <c r="H666" t="s">
+        <v>59</v>
+      </c>
+      <c r="I666" t="s">
+        <v>19</v>
+      </c>
+      <c r="J666" t="s">
+        <v>60</v>
+      </c>
+      <c r="K666" t="s">
+        <v>61</v>
+      </c>
+      <c r="L666" t="s">
+        <v>62</v>
+      </c>
+      <c r="M666" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A667" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B667" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D667" t="s">
+        <v>378</v>
+      </c>
+      <c r="E667" t="s">
+        <v>514</v>
+      </c>
+      <c r="F667" t="s">
+        <v>17</v>
+      </c>
+      <c r="G667">
+        <v>1</v>
+      </c>
+      <c r="H667" t="s">
+        <v>59</v>
+      </c>
+      <c r="I667" t="s">
+        <v>19</v>
+      </c>
+      <c r="J667" t="s">
+        <v>60</v>
+      </c>
+      <c r="K667" t="s">
+        <v>61</v>
+      </c>
+      <c r="L667" t="s">
+        <v>62</v>
+      </c>
+      <c r="M667" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A668" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B668" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C668" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D668" t="s">
+        <v>378</v>
+      </c>
+      <c r="E668" t="s">
+        <v>514</v>
+      </c>
+      <c r="F668" t="s">
+        <v>17</v>
+      </c>
+      <c r="G668">
+        <v>1</v>
+      </c>
+      <c r="H668" t="s">
+        <v>59</v>
+      </c>
+      <c r="I668" t="s">
+        <v>19</v>
+      </c>
+      <c r="J668" t="s">
+        <v>60</v>
+      </c>
+      <c r="K668" t="s">
+        <v>61</v>
+      </c>
+      <c r="L668" t="s">
+        <v>62</v>
+      </c>
+      <c r="M668" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A669" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B669" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D669" t="s">
+        <v>64</v>
+      </c>
+      <c r="E669" t="s">
+        <v>65</v>
+      </c>
+      <c r="F669" t="s">
+        <v>17</v>
+      </c>
+      <c r="G669">
+        <v>1</v>
+      </c>
+      <c r="H669" t="s">
+        <v>59</v>
+      </c>
+      <c r="I669" t="s">
+        <v>19</v>
+      </c>
+      <c r="J669" t="s">
+        <v>60</v>
+      </c>
+      <c r="K669" t="s">
+        <v>61</v>
+      </c>
+      <c r="L669" t="s">
+        <v>62</v>
+      </c>
+      <c r="M669" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A670" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B670" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C670" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D670" t="s">
+        <v>996</v>
+      </c>
+      <c r="E670" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F670" t="s">
+        <v>17</v>
+      </c>
+      <c r="G670">
+        <v>1</v>
+      </c>
+      <c r="H670" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I670" t="s">
+        <v>242</v>
+      </c>
+      <c r="J670" t="s">
+        <v>1763</v>
+      </c>
+      <c r="K670" t="s">
+        <v>1606</v>
+      </c>
+      <c r="L670" t="s">
+        <v>823</v>
+      </c>
+      <c r="M670" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A671" s="4" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B671" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D671" t="s">
+        <v>378</v>
+      </c>
+      <c r="E671" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F671" t="s">
+        <v>17</v>
+      </c>
+      <c r="G671">
+        <v>1</v>
+      </c>
+      <c r="H671" t="s">
+        <v>276</v>
+      </c>
+      <c r="I671" t="s">
+        <v>28</v>
+      </c>
+      <c r="J671" t="s">
+        <v>277</v>
+      </c>
+      <c r="K671" t="s">
+        <v>30</v>
+      </c>
+      <c r="L671" t="s">
+        <v>22</v>
+      </c>
+      <c r="M671" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A672" s="4" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B672" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D672" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E672" t="s">
+        <v>1767</v>
+      </c>
+      <c r="F672" t="s">
+        <v>17</v>
+      </c>
+      <c r="G672">
+        <v>1</v>
+      </c>
+      <c r="H672" t="s">
+        <v>904</v>
+      </c>
+      <c r="I672" t="s">
+        <v>242</v>
+      </c>
+      <c r="J672" t="s">
+        <v>905</v>
+      </c>
+      <c r="K672" t="s">
+        <v>906</v>
+      </c>
+      <c r="L672" t="s">
+        <v>62</v>
+      </c>
+      <c r="M672" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A673" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B673" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D673" t="s">
+        <v>996</v>
+      </c>
+      <c r="E673" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F673" t="s">
+        <v>17</v>
+      </c>
+      <c r="G673">
+        <v>1</v>
+      </c>
+      <c r="H673" t="s">
+        <v>841</v>
+      </c>
+      <c r="I673" t="s">
+        <v>19</v>
+      </c>
+      <c r="J673" t="s">
+        <v>842</v>
+      </c>
+      <c r="K673" t="s">
+        <v>61</v>
+      </c>
+      <c r="L673" t="s">
+        <v>22</v>
+      </c>
+      <c r="M673" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A674" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B674" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D674" t="s">
+        <v>128</v>
+      </c>
+      <c r="E674" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F674" t="s">
+        <v>17</v>
+      </c>
+      <c r="G674">
+        <v>1</v>
+      </c>
+      <c r="H674" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I674" t="s">
+        <v>19</v>
+      </c>
+      <c r="J674" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K674" t="s">
+        <v>860</v>
+      </c>
+      <c r="L674" t="s">
+        <v>38</v>
+      </c>
+      <c r="M674" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A675" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B675" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D675" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E675" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F675" t="s">
+        <v>17</v>
+      </c>
+      <c r="G675">
+        <v>1</v>
+      </c>
+      <c r="H675" t="s">
+        <v>636</v>
+      </c>
+      <c r="I675" t="s">
+        <v>19</v>
+      </c>
+      <c r="J675" t="s">
+        <v>637</v>
+      </c>
+      <c r="K675" t="s">
+        <v>638</v>
+      </c>
+      <c r="L675" t="s">
+        <v>38</v>
+      </c>
+      <c r="M675" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A676" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B676" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D676" t="s">
+        <v>828</v>
+      </c>
+      <c r="E676" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F676" t="s">
+        <v>17</v>
+      </c>
+      <c r="G676">
+        <v>1</v>
+      </c>
+      <c r="H676" t="s">
+        <v>1775</v>
+      </c>
+      <c r="I676" t="s">
+        <v>242</v>
+      </c>
+      <c r="J676" t="s">
+        <v>1776</v>
+      </c>
+      <c r="K676" t="s">
+        <v>1777</v>
+      </c>
+      <c r="L676" t="s">
+        <v>62</v>
+      </c>
+      <c r="M676" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A677" s="4" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B677" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D677" t="s">
+        <v>378</v>
+      </c>
+      <c r="E677" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F677" t="s">
+        <v>17</v>
+      </c>
+      <c r="G677">
+        <v>1</v>
+      </c>
+      <c r="H677" t="s">
+        <v>841</v>
+      </c>
+      <c r="I677" t="s">
+        <v>19</v>
+      </c>
+      <c r="J677" t="s">
+        <v>842</v>
+      </c>
+      <c r="K677" t="s">
+        <v>61</v>
+      </c>
+      <c r="L677" t="s">
+        <v>22</v>
+      </c>
+      <c r="M677" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A678" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B678" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D678" t="s">
+        <v>378</v>
+      </c>
+      <c r="E678" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F678" t="s">
+        <v>17</v>
+      </c>
+      <c r="G678">
+        <v>1</v>
+      </c>
+      <c r="H678" t="s">
+        <v>841</v>
+      </c>
+      <c r="I678" t="s">
+        <v>19</v>
+      </c>
+      <c r="J678" t="s">
+        <v>842</v>
+      </c>
+      <c r="K678" t="s">
+        <v>61</v>
+      </c>
+      <c r="L678" t="s">
+        <v>22</v>
+      </c>
+      <c r="M678" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A679" s="4" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B679" s="5">
+        <v>46289</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D679" t="s">
+        <v>554</v>
+      </c>
+      <c r="E679" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F679" t="s">
+        <v>17</v>
+      </c>
+      <c r="G679">
+        <v>1</v>
+      </c>
+      <c r="H679" t="s">
+        <v>488</v>
+      </c>
+      <c r="I679" t="s">
+        <v>19</v>
+      </c>
+      <c r="J679" t="s">
+        <v>489</v>
+      </c>
+      <c r="K679" t="s">
+        <v>490</v>
+      </c>
+      <c r="L679" t="s">
+        <v>38</v>
+      </c>
+      <c r="M679" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A680" s="4" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B680" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C680" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D680" t="s">
+        <v>554</v>
+      </c>
+      <c r="E680" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F680" t="s">
+        <v>17</v>
+      </c>
+      <c r="G680">
+        <v>1</v>
+      </c>
+      <c r="H680" t="s">
+        <v>211</v>
+      </c>
+      <c r="I680" t="s">
+        <v>28</v>
+      </c>
+      <c r="J680" t="s">
+        <v>212</v>
+      </c>
+      <c r="K680" t="s">
+        <v>213</v>
+      </c>
+      <c r="L680" t="s">
+        <v>38</v>
+      </c>
+      <c r="M680" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A681" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B681" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D681" t="s">
+        <v>33</v>
+      </c>
+      <c r="E681" t="s">
+        <v>966</v>
+      </c>
+      <c r="F681" t="s">
+        <v>17</v>
+      </c>
+      <c r="G681">
+        <v>1</v>
+      </c>
+      <c r="H681" t="s">
+        <v>684</v>
+      </c>
+      <c r="I681" t="s">
+        <v>19</v>
+      </c>
+      <c r="J681" t="s">
+        <v>685</v>
+      </c>
+      <c r="K681" t="s">
+        <v>467</v>
+      </c>
+      <c r="L681" t="s">
+        <v>38</v>
+      </c>
+      <c r="M681" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A682" s="4" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B682" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D682" t="s">
+        <v>554</v>
+      </c>
+      <c r="E682" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F682" t="s">
+        <v>17</v>
+      </c>
+      <c r="G682">
+        <v>1</v>
+      </c>
+      <c r="H682" t="s">
+        <v>230</v>
+      </c>
+      <c r="I682" t="s">
+        <v>19</v>
+      </c>
+      <c r="J682" t="s">
+        <v>231</v>
+      </c>
+      <c r="K682" t="s">
+        <v>232</v>
+      </c>
+      <c r="L682" t="s">
+        <v>38</v>
+      </c>
+      <c r="M682" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A683" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B683" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D683" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E683" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F683" t="s">
+        <v>17</v>
+      </c>
+      <c r="G683">
+        <v>1</v>
+      </c>
+      <c r="H683" t="s">
+        <v>230</v>
+      </c>
+      <c r="I683" t="s">
+        <v>19</v>
+      </c>
+      <c r="J683" t="s">
+        <v>231</v>
+      </c>
+      <c r="K683" t="s">
+        <v>232</v>
+      </c>
+      <c r="L683" t="s">
+        <v>38</v>
+      </c>
+      <c r="M683" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A684" s="4" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B684" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D684" t="s">
+        <v>554</v>
+      </c>
+      <c r="E684" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F684" t="s">
+        <v>17</v>
+      </c>
+      <c r="G684">
+        <v>1</v>
+      </c>
+      <c r="H684" t="s">
+        <v>211</v>
+      </c>
+      <c r="I684" t="s">
+        <v>28</v>
+      </c>
+      <c r="J684" t="s">
+        <v>212</v>
+      </c>
+      <c r="K684" t="s">
+        <v>213</v>
+      </c>
+      <c r="L684" t="s">
+        <v>38</v>
+      </c>
+      <c r="M684" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A685" s="4" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B685" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D685" t="s">
+        <v>554</v>
+      </c>
+      <c r="E685" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F685" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685">
+        <v>1</v>
+      </c>
+      <c r="H685" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I685" t="s">
+        <v>19</v>
+      </c>
+      <c r="J685" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K685" t="s">
+        <v>860</v>
+      </c>
+      <c r="L685" t="s">
+        <v>38</v>
+      </c>
+      <c r="M685" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A686" s="4" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B686" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D686" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E686" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F686" t="s">
+        <v>17</v>
+      </c>
+      <c r="G686">
+        <v>1</v>
+      </c>
+      <c r="H686" t="s">
+        <v>1793</v>
+      </c>
+      <c r="I686" t="s">
+        <v>19</v>
+      </c>
+      <c r="J686" t="s">
+        <v>1794</v>
+      </c>
+      <c r="K686" t="s">
+        <v>1795</v>
+      </c>
+      <c r="L686" t="s">
+        <v>38</v>
+      </c>
+      <c r="M686" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A687" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B687" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D687" t="s">
+        <v>554</v>
+      </c>
+      <c r="E687" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F687" t="s">
+        <v>17</v>
+      </c>
+      <c r="G687">
+        <v>1</v>
+      </c>
+      <c r="H687" t="s">
+        <v>488</v>
+      </c>
+      <c r="I687" t="s">
+        <v>19</v>
+      </c>
+      <c r="J687" t="s">
+        <v>489</v>
+      </c>
+      <c r="K687" t="s">
+        <v>490</v>
+      </c>
+      <c r="L687" t="s">
+        <v>38</v>
+      </c>
+      <c r="M687" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A688" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B688" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D688" t="s">
+        <v>197</v>
+      </c>
+      <c r="E688" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F688" t="s">
+        <v>17</v>
+      </c>
+      <c r="G688">
+        <v>1</v>
+      </c>
+      <c r="H688" t="s">
+        <v>636</v>
+      </c>
+      <c r="I688" t="s">
+        <v>19</v>
+      </c>
+      <c r="J688" t="s">
+        <v>637</v>
+      </c>
+      <c r="K688" t="s">
+        <v>638</v>
+      </c>
+      <c r="L688" t="s">
+        <v>38</v>
+      </c>
+      <c r="M688" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A689" s="4" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B689" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D689" t="s">
+        <v>197</v>
+      </c>
+      <c r="E689" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F689" t="s">
+        <v>17</v>
+      </c>
+      <c r="G689">
+        <v>1</v>
+      </c>
+      <c r="H689" t="s">
+        <v>636</v>
+      </c>
+      <c r="I689" t="s">
+        <v>19</v>
+      </c>
+      <c r="J689" t="s">
+        <v>637</v>
+      </c>
+      <c r="K689" t="s">
+        <v>638</v>
+      </c>
+      <c r="L689" t="s">
+        <v>38</v>
+      </c>
+      <c r="M689" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A690" s="4" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B690" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D690" t="s">
+        <v>197</v>
+      </c>
+      <c r="E690" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F690" t="s">
+        <v>17</v>
+      </c>
+      <c r="G690">
+        <v>1</v>
+      </c>
+      <c r="H690" t="s">
+        <v>636</v>
+      </c>
+      <c r="I690" t="s">
+        <v>19</v>
+      </c>
+      <c r="J690" t="s">
+        <v>637</v>
+      </c>
+      <c r="K690" t="s">
+        <v>638</v>
+      </c>
+      <c r="L690" t="s">
+        <v>38</v>
+      </c>
+      <c r="M690" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A691" s="4" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B691" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D691" t="s">
+        <v>554</v>
+      </c>
+      <c r="E691" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F691" t="s">
+        <v>17</v>
+      </c>
+      <c r="G691">
+        <v>1</v>
+      </c>
+      <c r="H691" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I691" t="s">
+        <v>19</v>
+      </c>
+      <c r="J691" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K691" t="s">
+        <v>773</v>
+      </c>
+      <c r="L691" t="s">
+        <v>384</v>
+      </c>
+      <c r="M691" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A692" s="4" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B692" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D692" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E692" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F692" t="s">
+        <v>17</v>
+      </c>
+      <c r="G692">
+        <v>1</v>
+      </c>
+      <c r="H692" t="s">
+        <v>130</v>
+      </c>
+      <c r="I692" t="s">
+        <v>19</v>
+      </c>
+      <c r="J692" t="s">
+        <v>131</v>
+      </c>
+      <c r="K692" t="s">
+        <v>132</v>
+      </c>
+      <c r="L692" t="s">
+        <v>38</v>
+      </c>
+      <c r="M692" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A693" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B693" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D693" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E693" t="s">
+        <v>368</v>
+      </c>
+      <c r="F693" t="s">
+        <v>17</v>
+      </c>
+      <c r="G693">
+        <v>3</v>
+      </c>
+      <c r="H693" t="s">
+        <v>252</v>
+      </c>
+      <c r="I693" t="s">
+        <v>19</v>
+      </c>
+      <c r="J693" t="s">
+        <v>253</v>
+      </c>
+      <c r="K693" t="s">
+        <v>254</v>
+      </c>
+      <c r="L693" t="s">
+        <v>38</v>
+      </c>
+      <c r="M693" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A694" s="4" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B694" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D694" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E694" t="s">
+        <v>352</v>
+      </c>
+      <c r="F694" t="s">
+        <v>17</v>
+      </c>
+      <c r="G694">
+        <v>1</v>
+      </c>
+      <c r="H694" t="s">
+        <v>353</v>
+      </c>
+      <c r="I694" t="s">
+        <v>19</v>
+      </c>
+      <c r="J694" t="s">
+        <v>354</v>
+      </c>
+      <c r="K694" t="s">
+        <v>355</v>
+      </c>
+      <c r="L694" t="s">
+        <v>38</v>
+      </c>
+      <c r="M694" s="6" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A695" s="4" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B695" s="5">
+        <v>46290</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D695" t="s">
+        <v>554</v>
+      </c>
+      <c r="E695" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F695" t="s">
+        <v>17</v>
+      </c>
+      <c r="G695">
+        <v>1</v>
+      </c>
+      <c r="H695" t="s">
+        <v>211</v>
+      </c>
+      <c r="I695" t="s">
+        <v>28</v>
+      </c>
+      <c r="J695" t="s">
+        <v>212</v>
+      </c>
+      <c r="K695" t="s">
+        <v>213</v>
+      </c>
+      <c r="L695" t="s">
+        <v>38</v>
+      </c>
+      <c r="M695" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A696" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B696" s="8">
+        <v>46290</v>
+      </c>
+      <c r="C696" s="8" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D696" s="9" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E696" s="9" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F696" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G696" s="9">
+        <v>1</v>
+      </c>
+      <c r="H696" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I696" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J696" s="9" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K696" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L696" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="M696" s="10" t="s">
+        <v>1717</v>
       </c>
     </row>
   </sheetData>
